--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486770_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486770_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.475</v>
+        <v>8.822900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9407</v>
+        <v>7.0651</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5343</v>
+        <v>1.7578</v>
       </c>
       <c r="G2" t="n">
         <v>6.7344</v>
@@ -610,13 +610,13 @@
         <v>1.3515</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1347</v>
+        <v>1.4826</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0959</v>
+        <v>1.2202</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0389</v>
+        <v>0.2624</v>
       </c>
       <c r="V2" t="n">
         <v>1.1851</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. EDOMWONYI IBRAHIM</t>
+          <t>A. NAVAS CERVERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2886</v>
+        <v>5.42</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9422</v>
+        <v>3.1732</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3464</v>
+        <v>2.2468</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9729</v>
+        <v>5.1649</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9037</v>
+        <v>3.648</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0692</v>
+        <v>1.517</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1261</v>
+        <v>4.67</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3529</v>
+        <v>4.1318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7732</v>
+        <v>0.5381</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1531</v>
+        <v>0.495</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4492</v>
+        <v>-0.4838</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2961</v>
+        <v>0.9788</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.1239</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7377</v>
+        <v>2.7031</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6592</v>
+        <v>0.9035</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2682</v>
+        <v>0.6271</v>
       </c>
       <c r="U3" t="n">
-        <v>1.391</v>
+        <v>0.2764</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0426</v>
+        <v>-1.2277</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3709</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.55</v>
+        <v>5.4009</v>
       </c>
       <c r="E4" t="n">
-        <v>2.933</v>
+        <v>3.5604</v>
       </c>
       <c r="F4" t="n">
-        <v>1.617</v>
+        <v>1.8405</v>
       </c>
       <c r="G4" t="n">
         <v>3.2425</v>
@@ -766,13 +766,13 @@
         <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0441</v>
+        <v>0.8069</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1657</v>
+        <v>0.4618</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1216</v>
+        <v>0.3451</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. NAVAS CERVERA</t>
+          <t>I. EDOMWONYI IBRAHIM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1802</v>
+        <v>4.0639</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1321</v>
+        <v>2.4872</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0481</v>
+        <v>1.5766</v>
       </c>
       <c r="G5" t="n">
-        <v>5.1649</v>
+        <v>2.9729</v>
       </c>
       <c r="H5" t="n">
-        <v>3.648</v>
+        <v>1.9037</v>
       </c>
       <c r="I5" t="n">
-        <v>1.517</v>
+        <v>1.0692</v>
       </c>
       <c r="J5" t="n">
-        <v>4.67</v>
+        <v>4.1261</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1318</v>
+        <v>3.3529</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5381</v>
+        <v>0.7732</v>
       </c>
       <c r="M5" t="n">
-        <v>0.495</v>
+        <v>-1.1531</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4838</v>
+        <v>-1.4492</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9788</v>
+        <v>0.2961</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5792</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q5" t="n">
         <v>-2.1239</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7031</v>
+        <v>1.7377</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3363</v>
+        <v>1.4345</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.414</v>
+        <v>0.8133</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.6212</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2277</v>
+        <v>0.0426</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.3282</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2277</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1282</v>
+        <v>1.876</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1325</v>
+        <v>0.7809</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9957</v>
+        <v>1.095</v>
       </c>
       <c r="G6" t="n">
         <v>5.2851</v>
@@ -922,13 +922,13 @@
         <v>2.1239</v>
       </c>
       <c r="S6" t="n">
-        <v>1.666</v>
+        <v>1.4138</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6544</v>
+        <v>1.3028</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0116</v>
+        <v>0.111</v>
       </c>
       <c r="V6" t="n">
         <v>-1.9268</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4781</v>
+        <v>1.3676</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4889</v>
+        <v>2.3784</v>
       </c>
       <c r="F7" t="n">
         <v>-1.0108</v>
@@ -1000,10 +1000,10 @@
         <v>1.5446</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8824</v>
+        <v>0.0071</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7174</v>
+        <v>0.1721</v>
       </c>
       <c r="U7" t="n">
         <v>-0.1651</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. ESTEBAN GLADER</t>
+          <t>P. JIMÉNEZ VELÁZQUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3899</v>
+        <v>-1.8042</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5465</v>
+        <v>-1.601</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1565</v>
+        <v>-0.2032</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5744</v>
+        <v>-2.6701</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4342</v>
+        <v>-1.5104</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1402</v>
+        <v>-1.1597</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.829</v>
+        <v>-1.8422</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9510999999999999</v>
+        <v>-0.5446</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1221</v>
+        <v>-1.2976</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7454</v>
+        <v>-0.8278</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4832</v>
+        <v>-0.9657</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2623</v>
+        <v>0.1379</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7377</v>
+        <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6053</v>
+        <v>0.1861</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2133</v>
+        <v>0.2412</v>
       </c>
       <c r="U8" t="n">
-        <v>0.392</v>
+        <v>-0.0551</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. JIMÉNEZ VELÁZQUEZ</t>
+          <t>I. ESTEBAN GLADER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.371</v>
+        <v>-1.8988</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1181</v>
+        <v>-1.8567</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2529</v>
+        <v>-0.0421</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.6701</v>
+        <v>-1.5744</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5104</v>
+        <v>-1.4342</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1597</v>
+        <v>-0.1402</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8422</v>
+        <v>-0.829</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5446</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2976</v>
+        <v>0.1221</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8278</v>
+        <v>-0.7454</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9657</v>
+        <v>-0.4832</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1379</v>
+        <v>-0.2623</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9654</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9654</v>
+        <v>1.7377</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3807</v>
+        <v>1.0963</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2759</v>
+        <v>0.903</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1048</v>
+        <v>0.1933</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4824</v>
+        <v>-3.5637</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6734</v>
+        <v>-1.9285</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.809</v>
+        <v>-1.6352</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5223</v>
@@ -1234,13 +1234,13 @@
         <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1984</v>
+        <v>0.1171</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8547</v>
+        <v>0.5996</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6563</v>
+        <v>-0.4825</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>18.8568</v>
+        <v>19.6846</v>
       </c>
       <c r="E11" t="n">
-        <v>13.2314</v>
+        <v>14.059</v>
       </c>
       <c r="F11" t="n">
-        <v>5.6253</v>
+        <v>5.625399999999999</v>
       </c>
       <c r="G11" t="n">
         <v>18.4836</v>
@@ -1282,7 +1282,7 @@
         <v>11.7242</v>
       </c>
       <c r="I11" t="n">
-        <v>6.759500000000001</v>
+        <v>6.759499999999999</v>
       </c>
       <c r="J11" t="n">
         <v>21.4932</v>
@@ -1303,7 +1303,7 @@
         <v>4.238200000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9656000000000002</v>
+        <v>-0.9656000000000001</v>
       </c>
       <c r="Q11" t="n">
         <v>-15.4464</v>
@@ -1312,13 +1312,13 @@
         <v>14.4808</v>
       </c>
       <c r="S11" t="n">
-        <v>6.6201</v>
+        <v>7.4479</v>
       </c>
       <c r="T11" t="n">
-        <v>5.5135</v>
+        <v>6.3411</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1066</v>
+        <v>1.1067</v>
       </c>
       <c r="V11" t="n">
         <v>-5.2816</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.3631</v>
+        <v>3.3841</v>
       </c>
       <c r="E12" t="n">
-        <v>4.5865</v>
+        <v>3.3454</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2234</v>
+        <v>0.0386</v>
       </c>
       <c r="G12" t="n">
         <v>2.0606</v>
@@ -1390,13 +1390,13 @@
         <v>2.8962</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0202</v>
+        <v>0.0411</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6543</v>
+        <v>0.4132</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6341</v>
+        <v>-0.3721</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2277</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.681</v>
+        <v>0.2176</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.5172</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2499</v>
+        <v>-0.2996</v>
       </c>
       <c r="G13" t="n">
         <v>-0.0555</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4082</v>
+        <v>-0.0551</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.1654</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1709</v>
+        <v>-0.2206</v>
       </c>
       <c r="V13" t="n">
         <v>0.3282</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0046</v>
+        <v>-0.0984</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0339</v>
+        <v>0.827</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0384</v>
+        <v>-0.9254</v>
       </c>
       <c r="G14" t="n">
         <v>-1.1081</v>
@@ -1546,13 +1546,13 @@
         <v>1.5446</v>
       </c>
       <c r="S14" t="n">
-        <v>0.011</v>
+        <v>-0.0828</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2753</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2643</v>
+        <v>-0.1513</v>
       </c>
       <c r="V14" t="n">
         <v>0.8995</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.0157</v>
+        <v>-1.0849</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2905</v>
+        <v>0.2266</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7252</v>
+        <v>-1.3115</v>
       </c>
       <c r="G15" t="n">
         <v>-2.3333</v>
@@ -1624,13 +1624,13 @@
         <v>1.9308</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6824</v>
+        <v>-0.7516</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8277</v>
+        <v>-0.3106</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8547</v>
+        <v>-0.441</v>
       </c>
       <c r="V15" t="n">
         <v>1.2277</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-4.2505</v>
+        <v>-3.4287</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.2656</v>
+        <v>-1.6451</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9849</v>
+        <v>-1.7836</v>
       </c>
       <c r="G16" t="n">
         <v>-3.4463</v>
@@ -1702,13 +1702,13 @@
         <v>2.8962</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.2562</v>
+        <v>-1.4344</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4899</v>
+        <v>-0.8694</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7663</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2856</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.8977</v>
+        <v>-3.6774</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.1174</v>
+        <v>-2.1866</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7803</v>
+        <v>-1.4908</v>
       </c>
       <c r="G17" t="n">
         <v>-3.1467</v>
@@ -1780,13 +1780,13 @@
         <v>1.7377</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4341</v>
+        <v>-0.2138</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7725</v>
+        <v>0.1582</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6615</v>
+        <v>-0.372</v>
       </c>
       <c r="V17" t="n">
         <v>1.2277</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.6603</v>
+        <v>-5.9457</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.2655</v>
+        <v>-3.9894</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3948</v>
+        <v>-1.9563</v>
       </c>
       <c r="G18" t="n">
         <v>-6.2467</v>
@@ -1858,13 +1858,13 @@
         <v>2.8962</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4249</v>
+        <v>-0.7103</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6889</v>
+        <v>-0.0351</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1138</v>
+        <v>-0.6753</v>
       </c>
       <c r="V18" t="n">
         <v>2.1698</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-7.0722</v>
+        <v>-6.1551</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.2377</v>
+        <v>-2.7206</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.8345</v>
+        <v>-3.4346</v>
       </c>
       <c r="G19" t="n">
         <v>-4.2078</v>
@@ -1936,13 +1936,13 @@
         <v>1.5446</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.2618</v>
+        <v>-1.3448</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.214</v>
+        <v>-0.6969</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0478</v>
+        <v>-0.6479</v>
       </c>
       <c r="V19" t="n">
         <v>0.9421</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-18.8569</v>
+        <v>-16.7885</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.625399999999998</v>
+        <v>-5.625499999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-13.2314</v>
+        <v>-11.1632</v>
       </c>
       <c r="G20" t="n">
         <v>-18.4838</v>
@@ -2014,13 +2014,13 @@
         <v>15.4463</v>
       </c>
       <c r="S20" t="n">
-        <v>-6.620000000000001</v>
+        <v>-4.551699999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1065</v>
+        <v>-1.1067</v>
       </c>
       <c r="U20" t="n">
-        <v>-5.5134</v>
+        <v>-3.4452</v>
       </c>
       <c r="V20" t="n">
         <v>5.281700000000001</v>
